--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Protezione civile.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Protezione civile.xlsx
@@ -152,7 +152,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Consulta il piano di protezione civile</t>
+    <t>Vai al servizio</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -427,8 +427,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">.
-All'interno del piano troverai indicazioni su come proteggere te stesso/a, la tua famiglia e la comunità in caso di emergenze.
-Per consultarlo, [visita questo sito](URL).</t>
+All'interno del piano troverai indicazioni su come proteggere te stesso/a, la tua famiglia e la comunità in caso di emergenze.</t>
     </r>
   </si>
   <si>
@@ -503,7 +502,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -594,6 +593,9 @@
     <t>-</t>
   </si>
   <si>
+    <t>Consulta il piano</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -611,7 +613,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -677,10 +679,6 @@
   <si>
     <t xml:space="preserve">Notizie dal territorio
 Utilizza questo messaggio per inviare informazioni utili alla cittadinanza non strettamente legate ad una emergenza in corso. Ad esempio, è possibile utilizzare questo messaggio per comunicare la chiusura delle scuole o nuove iniziative in materia di prevenzione.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1355,7 @@
         <v>77</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>77</v>
@@ -1371,7 +1369,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>55</v>
@@ -1391,7 +1389,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>77</v>
@@ -1403,7 +1401,7 @@
         <v>77</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" s="34" t="s">
         <v>77</v>
@@ -1411,47 +1409,47 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="34" t="s">
         <v>59</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" s="34" t="s">
         <v>59</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>55</v>
@@ -1460,10 +1458,10 @@
         <v>55</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>55</v>
